--- a/ig/nr-change-signes-vitaux-display/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/nr-change-signes-vitaux-display/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4835" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4834" uniqueCount="706">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:47:58+00:00</t>
+    <t>2023-11-28T12:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,6 +443,9 @@
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
 This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
   </si>
@@ -683,10 +686,6 @@
     <t>Moment de la mesure</t>
   </si>
   <si>
-    <t>Moment de la mesure
-Texte libre</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -1757,6 +1756,9 @@
   </si>
   <si>
     <t>Méthode de la mesure</t>
+  </si>
+  <si>
+    <t>Indicates the mechanism used to perform the observation.</t>
   </si>
   <si>
     <t>Only used if not implicit in code for Observation.code.</t>
@@ -3572,10 +3574,10 @@
         <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3625,7 +3627,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3660,10 +3662,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3686,16 +3688,16 @@
         <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3745,7 +3747,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3780,10 +3782,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3806,16 +3808,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3841,13 +3843,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3865,7 +3867,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3886,10 +3888,10 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>80</v>
@@ -3900,10 +3902,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3926,16 +3928,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3961,13 +3963,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3985,7 +3987,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -4006,10 +4008,10 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -4020,10 +4022,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4049,13 +4051,13 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4105,7 +4107,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -4140,10 +4142,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4166,16 +4168,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4201,13 +4203,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4225,7 +4227,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4260,14 +4262,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4286,16 +4288,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4345,7 +4347,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4369,7 +4371,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4380,14 +4382,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4406,16 +4408,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4465,7 +4467,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4500,10 +4502,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4532,7 +4534,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>117</v>
@@ -4585,7 +4587,7 @@
         <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4620,13 +4622,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
@@ -4648,13 +4650,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4705,7 +4707,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4740,13 +4742,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
@@ -4768,13 +4770,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4825,7 +4827,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4860,13 +4862,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>113</v>
@@ -4888,13 +4890,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>117</v>
@@ -4947,7 +4949,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4982,13 +4984,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -5010,10 +5012,10 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>213</v>
@@ -5067,7 +5069,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5612,7 +5614,7 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>249</v>
@@ -5771,7 +5773,7 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y27" t="s" s="2">
         <v>267</v>
@@ -5893,7 +5895,7 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y28" t="s" s="2">
         <v>267</v>
@@ -6216,7 +6218,7 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>281</v>
@@ -6818,7 +6820,7 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>312</v>
@@ -7343,7 +7345,7 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>353</v>
@@ -7666,7 +7668,7 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>281</v>
@@ -7788,7 +7790,7 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>281</v>
@@ -8390,7 +8392,7 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>312</v>
@@ -10210,7 +10212,7 @@
         <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>470</v>
@@ -10578,7 +10580,7 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>499</v>
@@ -10737,7 +10739,7 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y68" t="s" s="2">
         <v>510</v>
@@ -11060,7 +11062,7 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>281</v>
@@ -11662,7 +11664,7 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>312</v>
@@ -12187,7 +12189,7 @@
         <v>80</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
@@ -12427,7 +12429,7 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y82" t="s" s="2">
         <v>548</v>
@@ -12750,7 +12752,7 @@
         <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>281</v>
@@ -12787,7 +12789,7 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
@@ -12983,7 +12985,7 @@
         <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
@@ -12998,13 +13000,13 @@
         <v>560</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -13029,13 +13031,11 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -13074,10 +13074,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13088,10 +13088,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13206,10 +13206,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13326,10 +13326,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13352,7 +13352,7 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>281</v>
@@ -13389,11 +13389,11 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13446,10 +13446,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13568,10 +13568,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13594,16 +13594,16 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13653,7 +13653,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13671,27 +13671,27 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13714,16 +13714,16 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13773,7 +13773,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13791,27 +13791,27 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13834,19 +13834,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13895,7 +13895,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13907,7 +13907,7 @@
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
@@ -13916,10 +13916,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13930,10 +13930,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14048,10 +14048,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14168,14 +14168,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14197,10 +14197,10 @@
         <v>114</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>117</v>
@@ -14255,7 +14255,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14290,10 +14290,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14316,16 +14316,16 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14375,7 +14375,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14384,10 +14384,10 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
@@ -14396,10 +14396,10 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14410,10 +14410,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14436,16 +14436,16 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14495,7 +14495,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14504,10 +14504,10 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>80</v>
@@ -14516,10 +14516,10 @@
         <v>80</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>80</v>
@@ -14530,10 +14530,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14559,16 +14559,16 @@
         <v>262</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14593,13 +14593,13 @@
         <v>80</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>80</v>
@@ -14617,7 +14617,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14635,10 +14635,10 @@
         <v>80</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>534</v>
@@ -14652,10 +14652,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14681,16 +14681,16 @@
         <v>262</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14718,10 +14718,10 @@
         <v>253</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>80</v>
@@ -14739,7 +14739,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14757,10 +14757,10 @@
         <v>80</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>534</v>
@@ -14774,10 +14774,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14892,10 +14892,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15012,10 +15012,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15038,7 +15038,7 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>281</v>
@@ -15134,10 +15134,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15252,10 +15252,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15372,10 +15372,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15494,10 +15494,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15614,10 +15614,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15640,7 +15640,7 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>312</v>
@@ -15736,10 +15736,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15858,10 +15858,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15980,10 +15980,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16102,10 +16102,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16128,19 +16128,19 @@
         <v>80</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>80</v>
@@ -16189,7 +16189,7 @@
         <v>80</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -16201,7 +16201,7 @@
         <v>103</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>80</v>
@@ -16210,10 +16210,10 @@
         <v>80</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>80</v>
@@ -16224,10 +16224,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16253,10 +16253,10 @@
         <v>107</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>314</v>
@@ -16309,7 +16309,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16330,10 +16330,10 @@
         <v>80</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -16344,10 +16344,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16370,16 +16370,16 @@
         <v>92</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16429,7 +16429,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16450,10 +16450,10 @@
         <v>80</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -16464,10 +16464,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16490,16 +16490,16 @@
         <v>92</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16549,7 +16549,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16570,10 +16570,10 @@
         <v>80</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -16584,10 +16584,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16610,19 +16610,19 @@
         <v>92</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -16671,7 +16671,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16683,7 +16683,7 @@
         <v>103</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>80</v>
@@ -16692,10 +16692,10 @@
         <v>80</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -16706,10 +16706,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16824,10 +16824,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16944,14 +16944,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16973,10 +16973,10 @@
         <v>114</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>117</v>
@@ -17031,7 +17031,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -17066,10 +17066,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17095,16 +17095,16 @@
         <v>262</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -17129,7 +17129,7 @@
         <v>80</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y121" t="s" s="2">
         <v>353</v>
@@ -17153,7 +17153,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>91</v>
@@ -17171,7 +17171,7 @@
         <v>80</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>357</v>
@@ -17188,10 +17188,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17214,16 +17214,16 @@
         <v>92</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>444</v>
@@ -17254,10 +17254,10 @@
         <v>253</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>80</v>
@@ -17275,7 +17275,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17284,7 +17284,7 @@
         <v>91</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>104</v>
@@ -17293,7 +17293,7 @@
         <v>80</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>449</v>
@@ -17310,10 +17310,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17339,13 +17339,13 @@
         <v>262</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>509</v>
@@ -17373,7 +17373,7 @@
         <v>80</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y123" t="s" s="2">
         <v>510</v>
@@ -17397,7 +17397,7 @@
         <v>80</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17406,7 +17406,7 @@
         <v>91</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>104</v>
@@ -17432,10 +17432,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17495,10 +17495,10 @@
         <v>80</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="Z124" t="s" s="2">
         <v>531</v>
@@ -17519,7 +17519,7 @@
         <v>80</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17554,10 +17554,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17583,16 +17583,16 @@
         <v>81</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -17641,7 +17641,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17662,10 +17662,10 @@
         <v>80</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>
